--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:25 UTC</t>
+          <t>2026-09-24 17:06 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 16:25 UTC</t>
+          <t>2026-09-24 17:07 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 16:26 UTC</t>
+          <t>2026-09-24 17:07 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Forward Deployed Software Engineer - US Government</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Kitsap, WA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -610,27 +610,23 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://jobs.lever.co/palantir/a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +641,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 17:06 UTC</t>
+          <t>2026-09-24 21:40 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +663,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,7 +678,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California; New York, New York</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -692,32 +688,28 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +724,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:07 UTC</t>
+          <t>2026-09-24 21:40 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -746,96 +738,13 @@
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Palantir</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Forward Deployed Software Engineer - US Government</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Kitsap, WA</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>lever</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/palantir/a2e9ab0f-4dd1-4744-92b9-edc7ae393c58</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 17:07 UTC</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q4"/>
+  <autoFilter ref="A1:Q3"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -847,7 +756,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,19 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,17 +84,28 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -441,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -550,8 +577,1471 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Business Systems Engineer, Tech Foundations</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>8214444</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8214444?gh_jid=8214444</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA • New York, NY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>6143238004</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer, Airports</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8806570002</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Public Sector - New Grad</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>4736426005</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8805925002</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Thrive Intern</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>8806114002</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Asana</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Software Engineer, Developer Productivity</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8212172</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Nuro</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Mountain View, California (HQ)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>8180955</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern - Spring 2027</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6199367004</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Android (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>8142961</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142961?gh_jid=8142961&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Backend (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Bellevue, WA; Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8123225</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8123225?gh_jid=8123225&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, iOS (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>8142959</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142959?gh_jid=8142959&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Web (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8142963</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8142963?gh_jid=8142963&amp;t=gh_src%3D</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:25 UTC</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>R0250290</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Rome, NY</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>R0248386</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>R0248029</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27 23:28 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:Q18"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -560,6 +2050,25 @@
       <formula1>"Not Started,Applied,OA,Recruiter Screen,Interview,Rejected,Offer,Withdrawn"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:37 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Factored</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Airports</t>
+          <t>Staff AI Engineer</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8806570002</t>
+          <t>5425364008</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,22 +754,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Backend Software Engineer, Airports</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5425364008</t>
+          <t>8806570002</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Android (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8142961</t>
+          <t>6143238004</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142961?gh_jid=8142961&amp;t=gh_src%3D</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:37 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Backend (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1461,32 +1461,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8123225</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8123225?gh_jid=8123225&amp;t=gh_src%3D</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:38 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1533,57 +1533,53 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, iOS (Summer 2027)</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8142959</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142959?gh_jid=8142959&amp;t=gh_src%3D</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1598,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1620,27 +1616,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, Web (Summer 2027)</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1650,27 +1646,23 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8142963</t>
+          <t>R0248386</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8142963?gh_jid=8142963&amp;t=gh_src%3D</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1685,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 00:11 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1712,17 +1704,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1732,18 +1724,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>R0250290</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1753,7 +1745,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 00:14 UTC</t>
+          <t>2026-09-28 16:42 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1782,353 +1774,13 @@
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Figma</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA • New York, NY</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6143238004</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:11 UTC</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>4736426005</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:11 UTC</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Rome, NY</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>R0248386</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:14 UTC</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>R0248029</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:14 UTC</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q15"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2152,10 +1804,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:37 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Factored</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Staff AI Engineer</t>
+          <t>Backend Software Engineer, Airports</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Latin America</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>5425364008</t>
+          <t>8806570002</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/factored/jobs/5425364008</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, Airports</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8806570002</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8806570002?gh_jid=8806570002</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Duolingo</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8180955</t>
+          <t>8805925002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Duolingo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Intern - Spring 2027</t>
+          <t>Software Engineer, Thrive Intern</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6199367004</t>
+          <t>8806114002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
+          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Duolingo</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Senior Staff Software Engineer, Developer Productivity</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>New York, NY; Pittsburgh, PA; Seattle, WA</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8805925002</t>
+          <t>8212172</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/jobs/8805925002?gh_jid=8805925002</t>
+          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1102,12 +1102,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Duolingo</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Thrive Intern</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8806114002</t>
+          <t>8180955</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://careers.duolingo.com/jobs/8806114002?gh_jid=8806114002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Software Engineer, Developer Productivity</t>
+          <t>Software Engineering Intern - Spring 2027</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8212172</t>
+          <t>6199367004</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6199367004</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 18:56 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,57 +1359,53 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>6143238004</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6143238004?gh_jid=6143238004</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:37 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1446,22 +1442,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1471,32 +1467,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>R0248386</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1511,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 16:38 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1538,17 +1530,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1558,18 +1550,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>R0250290</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1579,7 +1571,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1594,7 +1586,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28 16:42 UTC</t>
+          <t>2026-09-28 19:01 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1608,179 +1600,13 @@
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Rome, NY</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>R0248386</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 16:42 UTC</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>R0248029</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28 16:42 UTC</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:Q13"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1802,8 +1628,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>Iambic Therapeutics, Inc</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Senior Staff Software Engineer, Developer Productivity</t>
+          <t>Software Engineer I/II - Scientific Computing</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Boston Office; Boston, MA, US</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -871,27 +871,23 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8212172</t>
+          <t>26e58057-83e9-46af-85eb-90142cf3b8ba</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
+          <t>https://jobs.ashbyhq.com/iambic-therapeutics/26e58057-83e9-46af-85eb-90142cf3b8ba</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Senior Staff Software Engineer, Developer Productivity</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,7 +939,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -953,28 +949,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8212172</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://www.asana.com/jobs/apply/8212172?gh_jid=8212172</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,27 +1011,27 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1041,23 +1041,23 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 17:51 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:06 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1181,57 +1181,53 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>R0250655</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1242,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01 17:46 UTC</t>
+          <t>2026-10-01 19:10 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1268,88 +1264,175 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Backend (Search)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Remote US</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8005406003</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 19:06 UTC</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Booz Allen Hamilton</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Security Engineer</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>El Segundo, CA</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 17:51 UTC</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 19:10 UTC</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q10"/>
+  <autoFilter ref="A1:Q11"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1368,6 +1451,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>New Grad Software Engineer, Routing</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,38 +856,42 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -902,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -939,42 +943,38 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:10 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1272,12 +1272,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer - New College Grad 2026</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>US, OR, Hillsboro</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1305,20 +1305,24 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>JR2017083</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05 19:12 UTC</t>
+          <t>2026-10-05 20:05 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,22 +1359,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Systems Software Engineer - New College Grad 2026</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>US, OR, Hillsboro</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1380,18 +1384,18 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>JR2017083</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 19:14 UTC</t>
+          <t>2026-10-05 20:08 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,17 +1447,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1463,63 +1467,146 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:10 UTC</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:14 UTC</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:10 UTC</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q13"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1540,6 +1627,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -605,22 +605,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Information Systems Security Engineer Level 3 (Government)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Columbia, Maryland, United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,23 +697,27 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>R-124625</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/columbia/information-systems-security-engineer-level-3-government/117/101580673696</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -728,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:22 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -750,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineer</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -765,32 +769,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8180955</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -815,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -837,12 +841,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Routing</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -852,32 +856,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -902,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -939,7 +943,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -974,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,12 +1015,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1026,38 +1030,42 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1072,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1094,12 +1102,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Public Sector - New Grad</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1109,32 +1117,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>4736426005</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1159,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1181,12 +1189,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1196,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1231,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1268,12 +1276,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Embedded Software Engineer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1283,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8180955</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1318,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8180955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,12 +1363,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>New Grad Software Engineer, Routing</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1370,12 +1378,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1385,17 +1393,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1405,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:19 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1450,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer - New College Grad 2026</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,38 +1465,38 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US, OR, Hillsboro</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>JR2017083</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1503,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 00:21 UTC</t>
+          <t>2026-10-06 17:35 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1525,22 +1533,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Systems Software Engineer - New College Grad 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>US, OR, Hillsboro</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1550,7 +1558,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1561,7 +1569,7 @@
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>JR2017083</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1571,7 +1579,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-OR-Hillsboro/Systems-Software-Engineer---New-College-Grad-2026_JR2017083</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1586,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 00:23 UTC</t>
+          <t>2026-10-06 17:38 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1608,27 +1616,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Senior Embedded Platform Engineer - Bootloader</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Palo Alto, CA, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1638,58 +1646,390 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>72155</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.ford.com/job/palo-alto/senior-embedded-platform-engineer-bootloader/48560/101614263632</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:38 UTC</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Sponsorship language in the posting is ambiguous or conditional.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, United States</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>72152</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.ford.com/job/dearborn/full-stack-data-engineer/48560/101614263584</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:38 UTC</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Sponsorship language in the posting is ambiguous or conditional.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>C++ Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Beavercreek, OH</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06 00:23 UTC</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:40 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q18"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1712,6 +2052,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:25 UTC</t>
+          <t>2026-10-07 17:36 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:25 UTC</t>
+          <t>2026-10-07 17:36 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:23 UTC</t>
+          <t>2026-10-07 17:34 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:27 UTC</t>
+          <t>2026-10-07 17:38 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:36 UTC</t>
+          <t>2026-10-07 18:09 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,22 +924,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Zekelman</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Intern, Automation Engineer</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, OH</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,23 +954,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>JR002792</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://zekelman.wd12.myworkdayjobs.com/Careers/job/Cambridge-OH/Intern--Automation-Engineer_JR002792</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:36 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1007,32 +1011,32 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1047,7 +1051,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1094,12 +1098,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1109,12 +1113,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1124,17 +1128,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>8227399</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1186,7 +1190,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1201,7 +1205,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1211,7 +1215,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1221,7 +1225,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1268,12 +1272,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1283,17 +1287,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1355,12 +1359,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1385,27 +1389,23 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1442,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,28 +1467,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1575,7 +1579,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1590,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1612,12 +1616,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1627,12 +1631,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1642,17 +1646,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1699,12 +1703,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1714,12 +1718,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1729,17 +1733,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1786,12 +1790,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1801,32 +1805,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1836,7 +1840,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1851,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Public Sector - New Grad</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1888,22 +1892,22 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>4736426005</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1923,7 +1927,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4736426005</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1942,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,7 +1969,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1975,32 +1979,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2025,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2047,12 +2051,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2062,42 +2066,38 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Spring 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,38 +2149,42 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>5252108007</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2199,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:38 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2217,12 +2221,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2232,32 +2236,32 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>5255111007</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2267,7 +2271,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2282,7 +2286,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:07 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2304,57 +2308,53 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Spring 2027 Software Engineering Internship/Co-op</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5252108007</t>
+          <t>R0250655</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2391,57 +2391,53 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Cybersecurity Engineer, Junior</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>5255111007</t>
+          <t>R0250290</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2456,7 +2452,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 17:34 UTC</t>
+          <t>2026-10-07 18:11 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2470,179 +2466,13 @@
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Product Engineering Intern</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>R0250655</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 17:38 UTC</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Cybersecurity Engineer, Junior</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Security Engineer</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>R0250290</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07 17:38 UTC</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q25"/>
+  <autoFilter ref="A1:Q23"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2674,8 +2504,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -697,23 +697,27 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>JR2025458</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -728,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:09 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -750,12 +754,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -780,27 +784,23 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>JR2025458</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:42 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:07 UTC</t>
+          <t>2026-10-07 18:39 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:11 UTC</t>
+          <t>2026-10-07 18:44 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:42 UTC</t>
+          <t>2026-10-07 19:14 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -924,22 +924,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Zekelman</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>Intern, Automation Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Cambridge, OH</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -954,27 +954,23 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>JR002792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://zekelman.wd12.myworkdayjobs.com/Careers/job/Cambridge-OH/Intern--Automation-Engineer_JR002792</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:14 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,32 +1007,32 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1061,7 +1057,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1098,12 +1094,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1113,12 +1109,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1128,7 +1124,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1138,7 +1134,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8227399</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1148,7 +1144,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:11 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1190,7 +1186,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, Performance Tooling and Infrastructure New Grad</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1205,7 +1201,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1215,17 +1211,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8227399</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8227399</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1272,12 +1268,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1287,17 +1283,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1312,7 +1308,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1322,7 +1318,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1337,7 +1333,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1359,12 +1355,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1374,7 +1370,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1389,23 +1385,27 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1442,12 +1442,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1467,32 +1467,28 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1507,7 +1503,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1544,7 +1540,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1579,7 +1575,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1594,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1616,12 +1612,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1631,12 +1627,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1646,17 +1642,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1666,7 +1662,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1703,12 +1699,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1718,12 +1714,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1733,17 +1729,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1753,7 +1749,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1790,12 +1786,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1805,22 +1801,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1830,7 +1826,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1840,7 +1836,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1855,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:11 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1882,7 +1878,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1897,7 +1893,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1917,7 +1913,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1927,7 +1923,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1942,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1969,7 +1965,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1979,7 +1975,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1989,22 +1985,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2014,7 +2010,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2029,7 +2025,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2051,12 +2047,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Staff Software Engineer, Backend (Search)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2066,12 +2062,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2081,23 +2077,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>8005406003</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:44 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2134,12 +2134,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Spring 2027 Software Engineering Internship/Co-op</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,42 +2149,38 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Co-op</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5252108007</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2199,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:16 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2226,7 +2222,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+          <t>Spring 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2261,7 +2257,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>5255111007</t>
+          <t>5252108007</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2271,7 +2267,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2286,7 +2282,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 18:39 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2308,53 +2304,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Palo Alto, CA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Co-op</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>5255111007</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:44 UTC</t>
+          <t>2026-10-07 19:12 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer, Junior</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2416,63 +2416,146 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
+          <t>R0250655</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:16 UTC</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Cybersecurity Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>R0250290</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Cybersecurity-Engineer--Junior_R0250290</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07 18:44 UTC</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:16 UTC</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q23"/>
+  <autoFilter ref="A1:Q24"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2504,6 +2587,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:44 UTC</t>
+          <t>2026-10-08 17:23 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 16:47 UTC</t>
+          <t>2026-10-08 17:25 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1907,13 +1907,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 16:48 UTC</t>
+          <t>2026-10-08 17:27 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,63 +1985,146 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:27 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
           <t>R0250655</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08 16:48 UTC</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 17:27 UTC</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q18"/>
+  <autoFilter ref="A1:Q19"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2068,6 +2151,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -605,22 +605,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -697,27 +697,23 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +728,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:13 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -754,22 +750,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Data Engineer - Talent Acquisition Operations</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,27 +780,23 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>1b690123-1766-4e75-a0ef-0f58afa864b4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://jobs.lever.co/palantir/1b690123-1766-4e75-a0ef-0f58afa864b4</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +811,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -841,12 +833,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,12 +848,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -871,17 +863,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +883,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +898,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -928,12 +920,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,17 +935,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -963,12 +955,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +970,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +985,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1015,27 +1007,27 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Security Engineer Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1045,17 +1037,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>4719593006</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1057,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1072,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1102,12 +1094,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,7 +1109,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1132,17 +1124,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1144,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1159,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1189,12 +1181,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,17 +1196,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1229,7 +1221,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1276,12 +1268,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,12 +1283,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1306,27 +1298,23 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>JR2025458</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1329,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:11 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1363,27 +1351,27 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1398,12 +1386,12 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1401,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1416,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1450,12 +1438,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1453,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,27 +1468,23 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1499,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1537,12 +1521,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,12 +1536,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,7 +1551,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1577,7 +1561,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1571,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1586,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1624,12 +1608,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,12 +1623,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1664,7 +1648,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1658,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1673,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1711,12 +1695,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Mobile (Winter 2027)</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,38 +1710,42 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California; New York, New York; New York, New York, United States; San Francisco, California, United States</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/2b587e66-deac-421a-a824-9415ba78b5a7</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1772,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:23 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1794,12 +1782,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1809,12 +1797,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1827,20 +1815,24 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>JR2025458</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1855,7 +1847,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:25 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1877,12 +1869,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1892,38 +1884,42 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1934,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 17:27 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1960,12 +1956,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1975,38 +1971,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 17:27 UTC</t>
+          <t>2026-10-08 18:09 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2043,88 +2043,258 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Staff Software Engineer, Backend (Search)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Remote US</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>8005406003</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:09 UTC</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Booz Allen Hamilton</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>C++ Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Beavercreek, OH</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>R0240412</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:13 UTC</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Product Engineering Intern</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Product Engineer</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>McLean, VA</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>R0250655</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08 17:27 UTC</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:13 UTC</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q19"/>
+  <autoFilter ref="A1:Q21"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2152,6 +2322,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:34 UTC</t>
+          <t>2026-10-11 16:59 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:36 UTC</t>
+          <t>2026-10-11 17:01 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:36 UTC</t>
+          <t>2026-10-11 17:01 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:38 UTC</t>
+          <t>2026-10-11 17:03 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:38 UTC</t>
+          <t>2026-10-11 17:03 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:38 UTC</t>
+          <t>2026-10-11 17:03 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:38 UTC</t>
+          <t>2026-10-11 17:03 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern [Winter 2027]</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>4719593006</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4719593006</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,32 +1465,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, AI Security</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Bellevue, WA; Menlo Park, CA</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8220757</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8220757?gh_jid=8220757&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Security</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8220757</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8220757?gh_jid=8220757&amp;t=gh_src%3D</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:35 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,19 +1878,19 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1915,27 +1915,23 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>JR2027337</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1950,7 +1946,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 16:59 UTC</t>
+          <t>2026-10-12 20:37 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1965,7 +1961,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 17:01 UTC</t>
+          <t>2026-10-12 20:37 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2048,7 +2044,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 17:01 UTC</t>
+          <t>2026-10-12 20:37 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2131,7 +2127,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 17:03 UTC</t>
+          <t>2026-10-12 20:39 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2214,7 +2210,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2278,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 17:03 UTC</t>
+          <t>2026-10-12 20:39 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2297,7 +2293,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11 17:03 UTC</t>
+          <t>2026-10-12 20:39 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2380,7 +2376,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2444,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11 17:03 UTC</t>
+          <t>2026-10-12 20:39 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2463,7 +2459,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,32 +595,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>6219995004</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:35 UTC</t>
+          <t>2026-10-13 18:39 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:37 UTC</t>
+          <t>2026-10-13 18:41 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:37 UTC</t>
+          <t>2026-10-13 18:41 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:37 UTC</t>
+          <t>2026-10-13 18:41 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>AI Software Developer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>R0248284</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:39 UTC</t>
+          <t>2026-10-13 18:43 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AI Software Developer, Junior</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2247,13 +2247,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>R0248284</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 20:39 UTC</t>
+          <t>2026-10-13 18:43 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2305,17 +2305,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>Product Engineering Intern</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2325,18 +2325,18 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>R0250655</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 20:39 UTC</t>
+          <t>2026-10-13 18:43 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2376,95 +2376,12 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Product Engineering Intern</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>McLean, VA</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>R0250655</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12 20:39 UTC</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q23"/>
+  <autoFilter ref="A1:Q22"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2495,7 +2412,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:09 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:39 UTC</t>
+          <t>2026-10-14 16:10 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1915,13 +1915,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2027337</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:41 UTC</t>
+          <t>2026-10-14 16:12 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Infrastructure Tools - New College Grad 2027</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1998,13 +1998,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>JR2027431</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/C---Software-Engineer--Infrastructure-Tools---New-College-Grad-2027_JR2027431</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:41 UTC</t>
+          <t>2026-10-14 16:12 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Systems Software Engineer, AI and Cloud - New College Grad 2026</t>
+          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2081,13 +2081,13 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>JR2025458</t>
+          <t>JR2027337</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Systems-Software-Engineer---AI-and-Cloud---New-College-Grad-2026_JR2025458</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:41 UTC</t>
+          <t>2026-10-14 16:12 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2127,19 +2127,19 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AI Software Developer, Junior</t>
+          <t>C++ Software Engineer, Infrastructure Tools - New College Grad 2027</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2164,13 +2164,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0248284</t>
+          <t>JR2027431</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/C---Software-Engineer--Infrastructure-Tools---New-College-Grad-2027_JR2027431</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:43 UTC</t>
+          <t>2026-10-14 16:12 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>AI Software Developer, Junior</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2247,13 +2247,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>R0248284</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 18:43 UTC</t>
+          <t>2026-10-14 16:14 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2305,17 +2305,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineering Intern</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2325,18 +2325,18 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>R0250655</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Product-Engineering-Intern_R0250655</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 18:43 UTC</t>
+          <t>2026-10-14 16:14 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Backend (Search)</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8005406003</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8005406003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:09 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,19 +1182,19 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Embedded Software Engineering Intern, Platform</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8887222002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8887222002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,32 +1465,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Khan Academy</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Remote (US + Canada Only)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8250259</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Security</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Bellevue, WA; Menlo Park, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8220757</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8220757?gh_jid=8220757&amp;t=gh_src%3D</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:10 UTC</t>
+          <t>2026-10-15 15:57 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12 UTC</t>
+          <t>2026-10-15 15:59 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12 UTC</t>
+          <t>2026-10-15 15:59 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12 UTC</t>
+          <t>2026-10-15 15:59 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2127,19 +2127,19 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Infrastructure Tools - New College Grad 2027</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2164,13 +2164,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>JR2027431</t>
+          <t>R0251725</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/C---Software-Engineer--Infrastructure-Tools---New-College-Grad-2027_JR2027431</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:12 UTC</t>
+          <t>2026-10-15 16:02 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:14 UTC</t>
+          <t>2026-10-15 16:02 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:14 UTC</t>
+          <t>2026-10-15 16:02 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8011590003</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8008645003</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,19 +1182,19 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern, Platform</t>
+          <t>Software Engineer, Infrastructure Platform</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8859182002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Embedded Software Engineering Intern, Platform</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8887222002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8887222002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:45 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:46 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:46 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:46 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:46 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:57 UTC</t>
+          <t>2026-10-16 15:46 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:59 UTC</t>
+          <t>2026-10-16 15:48 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:59 UTC</t>
+          <t>2026-10-16 15:48 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:59 UTC</t>
+          <t>2026-10-16 15:48 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 16:02 UTC</t>
+          <t>2026-10-16 15:50 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 16:02 UTC</t>
+          <t>2026-10-16 15:50 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 16:02 UTC</t>
+          <t>2026-10-16 15:50 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2376,12 +2376,186 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SpaceXSI</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Spring 2027 Software Engineering Internship/Co-op</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Co-op</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>5252108007</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:46 UTC</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SpaceXSI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Summer 2027 Software Engineering Internship/Co-op</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Co-op</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>5255111007</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:46 UTC</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q22"/>
+  <autoFilter ref="A1:Q24"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2412,6 +2586,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8011590003</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8011590003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer (Machine Learning) Intern (Summer 2027)</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8008645003</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008645003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1214,22 +1214,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Platform</t>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8859182002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8859182002?gh_jid=8859182002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern, Platform</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:46 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Khan Academy</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Remote (US + Canada Only)</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8250259</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/khanacademy/jobs/8250259</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:46 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:46 UTC</t>
+          <t>2026-10-17 14:38 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1741,27 +1741,23 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1772,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:46 UTC</t>
+          <t>2026-10-17 14:40 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,19 +1787,19 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1813,12 +1809,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1828,27 +1824,23 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1863,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:46 UTC</t>
+          <t>2026-10-17 14:40 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1878,7 +1870,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1882,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1915,13 +1907,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>JR2027337</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1931,7 +1923,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:48 UTC</t>
+          <t>2026-10-17 14:40 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1961,19 +1953,19 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>University, Software Engineer Intern</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1983,7 +1975,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Fayetteville, NC</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1993,18 +1985,18 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>R0251802</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2014,7 +2006,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2029,7 +2021,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:48 UTC</t>
+          <t>2026-10-17 14:41 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2044,19 +2036,19 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2066,7 +2058,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2081,13 +2073,13 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>JR2027337</t>
+          <t>R0251725</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2097,7 +2089,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2112,7 +2104,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:48 UTC</t>
+          <t>2026-10-17 14:41 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2127,7 +2119,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2131,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>AI Software Developer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2149,7 +2141,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2164,13 +2156,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0251725</t>
+          <t>R0248284</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2180,7 +2172,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2195,7 +2187,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:50 UTC</t>
+          <t>2026-10-17 14:41 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2210,7 +2202,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2214,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AI Software Developer, Junior</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2232,7 +2224,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2247,13 +2239,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>R0248284</t>
+          <t>R0240412</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2263,7 +2255,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2278,7 +2270,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16 15:50 UTC</t>
+          <t>2026-10-17 14:41 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2293,269 +2285,12 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>C++ Software Engineer, Junior</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Beavercreek, OH</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>R0240412</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:50 UTC</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SpaceXSI</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Spring 2027 Software Engineering Internship/Co-op</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Co-op</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>5252108007</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5252108007</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:46 UTC</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SpaceXSI</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2027 Software Engineering Internship/Co-op</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>On-site</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Co-op</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>5255111007</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/xai/jobs/5255111007</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:46 UTC</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q24"/>
+  <autoFilter ref="A1:Q21"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2585,9 +2320,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:38 UTC</t>
+          <t>2026-10-18 15:05 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:40 UTC</t>
+          <t>2026-10-18 15:07 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:40 UTC</t>
+          <t>2026-10-18 15:07 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:40 UTC</t>
+          <t>2026-10-18 15:07 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:41 UTC</t>
+          <t>2026-10-18 15:09 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:41 UTC</t>
+          <t>2026-10-18 15:09 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 14:41 UTC</t>
+          <t>2026-10-18 15:09 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17 14:41 UTC</t>
+          <t>2026-10-18 15:09 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
+          <t>Staff Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,32 +595,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6219995004</t>
+          <t>8257909</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
+          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:56 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,19 +660,19 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,32 +682,32 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>6219995004</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:56 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,19 +747,19 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:56 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,54 +1008,54 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
@@ -1214,22 +1214,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>New Grad Software Engineer, Product Engineering</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>8248317</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:05 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1741,23 +1741,27 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1772,7 +1776,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:07 UTC</t>
+          <t>2026-10-19 17:57 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1787,7 +1791,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1803,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1830,7 +1834,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1840,7 +1844,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:07 UTC</t>
+          <t>2026-10-19 17:59 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1870,7 +1874,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1886,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1907,13 +1911,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2027337</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1923,7 +1927,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1938,7 +1942,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:07 UTC</t>
+          <t>2026-10-19 17:59 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1953,19 +1957,19 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1975,7 +1979,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1985,18 +1989,18 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>R0251802</t>
+          <t>JR2027337</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2006,7 +2010,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:09 UTC</t>
+          <t>2026-10-19 17:59 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2036,7 +2040,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>University, Software Engineer Intern</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2058,7 +2062,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Fayetteville, NC</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2068,18 +2072,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0251725</t>
+          <t>R0251802</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2104,7 +2108,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:09 UTC</t>
+          <t>2026-10-19 18:01 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2119,7 +2123,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2135,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AI Software Developer, Junior</t>
+          <t>C++ Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2141,7 +2145,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Beavercreek, OH</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2156,13 +2160,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0248284</t>
+          <t>R0251725</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2172,7 +2176,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2187,7 +2191,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18 15:09 UTC</t>
+          <t>2026-10-19 18:01 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2202,7 +2206,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2218,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>AI Software Developer, Junior</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2224,7 +2228,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2239,13 +2243,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>R0240412</t>
+          <t>R0248284</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2255,7 +2259,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0240412</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18 15:09 UTC</t>
+          <t>2026-10-19 18:01 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2285,7 +2289,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Staff Software Engineer, Cloud Infrastructure</t>
+          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,32 +595,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8257909</t>
+          <t>6219995004</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8257909?gh_jid=8257909</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:56 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,19 +660,19 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
+          <t>Software Engineer, Platform Access (L2)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,32 +682,32 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6219995004</t>
+          <t>8026211</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:56 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,19 +747,19 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Software Engineer, Early Career (NYC)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>8008649003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:56 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Software Engineer, Early Career (SF)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>8010617003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,54 +1008,54 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8817974002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1214,22 +1214,22 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,54 +1269,54 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Nuro</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer, Software Updates</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Mountain View, California (HQ)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8230855</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>New Grad Software Engineer, Product Engineering</t>
+          <t>Software Engineer, Web3 Backend</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>Menlo Park, CA; New York, NY</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8248317</t>
+          <t>8258305</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8248317</t>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,42 +1639,38 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1689,7 +1685,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1704,19 +1700,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1726,12 +1722,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1741,27 +1737,23 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1776,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:57 UTC</t>
+          <t>2026-10-20 16:01 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1791,7 +1783,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59 UTC</t>
+          <t>2026-10-20 16:04 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1874,7 +1866,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1934,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59 UTC</t>
+          <t>2026-10-20 16:04 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1957,7 +1949,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2017,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 17:59 UTC</t>
+          <t>2026-10-20 16:04 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2040,7 +2032,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2044,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>Software Developer, Junior</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2062,7 +2054,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>Aberdeen Proving Ground, MD</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2072,18 +2064,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0251802</t>
+          <t>R0251954</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2093,7 +2085,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2108,7 +2100,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 18:01 UTC</t>
+          <t>2026-10-20 16:06 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2123,7 +2115,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2127,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>C++ Software Engineer, Junior</t>
+          <t>University, Software Engineer Intern</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2145,7 +2137,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Beavercreek, OH</t>
+          <t>Fayetteville, NC</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2155,18 +2147,18 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0251725</t>
+          <t>R0251802</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2176,7 +2168,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Beavercreek-OH/C---Software-Engineer--Junior_R0251725</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2191,7 +2183,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19 18:01 UTC</t>
+          <t>2026-10-20 16:06 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2206,7 +2198,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2266,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 18:01 UTC</t>
+          <t>2026-10-20 16:06 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2289,7 +2281,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:17 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,19 +660,19 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform Access (L2)</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -692,22 +692,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8026211</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8026211</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,29 +747,29 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (NYC)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8008649003</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8008649003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,19 +834,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Early Career (SF)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, California, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8010617003</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8010617003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,19 +921,19 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,34 +1008,34 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PhD Machine Learning Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1132,27 +1132,23 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8817974002</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8817974002?gh_jid=8817974002</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1163,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,29 +1178,29 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Software Engineer, New Grad - Query Engines</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1219,27 +1215,23 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:18 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1261,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,7 +1283,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1301,32 +1293,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>JR2028350</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1329,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:20 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1344,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,7 +1366,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1393,27 +1381,23 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1412,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:20 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1427,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Nuro</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Updates</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1449,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mountain View, California (HQ)</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,27 +1464,23 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8230855</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://nuro.ai/careersitem?gh_jid=8230855</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1495,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:20 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,34 +1510,34 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Web3 Backend</t>
+          <t>Model-Based Systems Engineer, Junior</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA; New York, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,27 +1547,23 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>8258305</t>
+          <t>R0249353</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/8258305?gh_jid=8258305&amp;t=gh_src%3D</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1578,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:22 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,19 +1593,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Software Developer, Junior</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1639,38 +1615,38 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Aberdeen Proving Ground, MD</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>R0251954</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1685,7 +1661,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:22 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1700,19 +1676,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>University, Software Engineer Intern</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1722,38 +1698,38 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Fayetteville, NC</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>R0251802</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1744,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20 16:01 UTC</t>
+          <t>2026-10-21 16:22 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1783,510 +1759,12 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>US, CA, Santa Clara</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>JR2026744</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:04 UTC</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>US, CA, Santa Clara</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>JR2027552</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:04 UTC</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer, DL Kernel Libraries - New College Grad 2027</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>US, CA, Santa Clara</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>JR2027337</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--DL-Kernel-Libraries---New-College-Grad-2027_JR2027337</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:04 UTC</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Software Developer, Junior</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Aberdeen Proving Ground, MD</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>R0251954</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:06 UTC</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>University, Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Fayetteville, NC</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>R0251802</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:06 UTC</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>AI Software Developer, Junior</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>San Diego, CA</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>R0248284</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/AI-Software-Developer--Junior_R0248284</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20 16:06 UTC</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q21"/>
+  <autoFilter ref="A1:Q15"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2310,12 +1788,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
+          <t>Software Engineer, DevAI</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,32 +595,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6219995004</t>
+          <t>8280222</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
+          <t>https://careers.airbnb.com/positions/8280222?gh_jid=8280222</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:17 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,19 +660,19 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -682,12 +682,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>6219995004</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,29 +747,29 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Analyst, Early Career (Full Stack)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8039471003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,54 +834,54 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>Software Engineer I, Fullstack (Search)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,54 +921,54 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,19 +1008,19 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1132,23 +1132,27 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1178,19 +1182,19 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1200,12 +1204,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1215,23 +1219,27 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:18 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1261,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1283,7 +1291,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1298,23 +1306,27 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>JR2028350</t>
+          <t>8879673002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1329,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:20 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1344,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1366,38 +1378,38 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1412,7 +1424,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:20 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1427,19 +1439,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1449,12 +1461,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1464,23 +1476,23 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1495,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:20 UTC</t>
+          <t>2026-10-22 16:19 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1510,29 +1522,29 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1553,7 +1565,7 @@
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>R0249353</t>
+          <t>JR2028350</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1563,7 +1575,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1578,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 16:22 UTC</t>
+          <t>2026-10-22 16:22 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1593,19 +1605,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Developer, Junior</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1615,7 +1627,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1630,13 +1642,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>R0251954</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1646,7 +1658,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1661,7 +1673,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 16:22 UTC</t>
+          <t>2026-10-22 16:22 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1676,19 +1688,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1698,7 +1710,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1708,63 +1720,482 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
+          <t>JR2027552</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:22 UTC</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Process Specialist-Tooling Engineer</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Sterling Heights, MI, United States</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72859</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.careers.ford.com/en/job/sterling-heights/process-specialist-tooling-engineer/48560/102290232800</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:21 UTC</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Not Supported</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Current job posting states that visa sponsorship is unavailable.</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Model-Based Systems Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>R0249353</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:23 UTC</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer, Junior</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen Proving Ground, MD</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>R0251954</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:23 UTC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>University, Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Fayetteville, NC</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
           <t>R0251802</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-21 16:22 UTC</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:23 UTC</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3Cloud</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Architect - DevOps</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8904100002</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/3cloud/jobs/8904100002?gh_jid=8904100002</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19 UTC</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Not Supported</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Current job posting states that visa sponsorship is unavailable.</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:Q20"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -1788,6 +2219,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,12 +580,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, DevAI</t>
+          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,32 +595,32 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8280222</t>
+          <t>6219995004</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/8280222?gh_jid=8280222</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,54 +660,54 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
+          <t>Analyst, Early Career (Full Stack)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6219995004</t>
+          <t>8039471003</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -759,42 +759,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Analyst, Early Career (Full Stack)</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States; San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8039471003</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,54 +834,54 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -933,17 +933,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,54 +1008,54 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,19 +1095,19 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8906750002</t>
+          <t>8886748002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8879673002</t>
+          <t>8886605002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8879673002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Software Engineer - Mercury Command</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,38 +1378,42 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>6233238004</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1455,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1476,13 +1480,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1492,7 +1496,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1507,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1522,19 +1526,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
+          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1544,12 +1548,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1559,23 +1563,23 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>JR2028350</t>
+          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
+          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1590,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:22 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1605,19 +1609,19 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1627,38 +1631,38 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1673,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:22 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1688,19 +1692,19 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1710,12 +1714,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1725,23 +1729,23 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1756,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:22 UTC</t>
+          <t>2026-10-23 16:17 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1771,34 +1775,34 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Process Specialist-Tooling Engineer</t>
+          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, United States</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1808,23 +1812,23 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72859</t>
+          <t>JR2028350</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://www.careers.ford.com/en/job/sterling-heights/process-specialist-tooling-engineer/48560/102290232800</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1839,44 +1843,44 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:21 UTC</t>
+          <t>2026-10-23 16:20 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Not Supported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Current job posting states that visa sponsorship is unavailable.</t>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1891,13 +1895,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>R0249353</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1907,7 +1911,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1922,7 +1926,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:23 UTC</t>
+          <t>2026-10-23 16:20 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1937,19 +1941,19 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Software Developer, Junior</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1959,7 +1963,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1974,13 +1978,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>R0251954</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2005,7 +2009,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:23 UTC</t>
+          <t>2026-10-23 16:20 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2020,7 +2024,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2032,17 +2036,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>Model-Based Systems Engineer, Junior</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2052,18 +2056,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0251802</t>
+          <t>R0249353</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2088,7 +2092,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 16:23 UTC</t>
+          <t>2026-10-23 16:22 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2103,34 +2107,34 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3Cloud</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Architect - DevOps</t>
+          <t>Software Developer, Junior</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Aberdeen Proving Ground, MD</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2140,27 +2144,23 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8904100002</t>
+          <t>R0251954</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/3cloud/jobs/8904100002?gh_jid=8904100002</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2175,27 +2175,110 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 16:19 UTC</t>
+          <t>2026-10-23 16:22 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Not Supported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Current job posting states that visa sponsorship is unavailable.</t>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>University, Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Fayetteville, NC</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>R0251802</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 16:22 UTC</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q20"/>
+  <autoFilter ref="A1:Q21"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2224,6 +2307,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Supported</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+          <t>Current job posting states that visa sponsorship is unavailable.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:17 UTC</t>
+          <t>2026-10-24 15:03 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:20 UTC</t>
+          <t>2026-10-24 15:05 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:20 UTC</t>
+          <t>2026-10-24 15:05 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:20 UTC</t>
+          <t>2026-10-24 15:05 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:22 UTC</t>
+          <t>2026-10-24 15:07 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 16:22 UTC</t>
+          <t>2026-10-24 15:07 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 16:22 UTC</t>
+          <t>2026-10-24 15:07 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:03 UTC</t>
+          <t>2026-10-25 15:14 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:05 UTC</t>
+          <t>2026-10-25 15:17 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:05 UTC</t>
+          <t>2026-10-25 15:17 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:05 UTC</t>
+          <t>2026-10-25 15:17 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:07 UTC</t>
+          <t>2026-10-25 15:18 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24 15:07 UTC</t>
+          <t>2026-10-25 15:18 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24 15:07 UTC</t>
+          <t>2026-10-25 15:18 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:04 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:04 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:04 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:04 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:04 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8906750002</t>
+          <t>8917377002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8886748002</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8886605002</t>
+          <t>8886748002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Mercury Command</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>6233238004</t>
+          <t>8886605002</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
+          <t>Software Engineer - Mercury Command</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,23 +1480,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>6233238004</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1511,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1526,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1542,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
+          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1569,7 +1573,7 @@
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1579,7 +1583,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1594,7 +1598,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1609,7 +1613,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1625,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1641,18 +1645,18 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1692,7 +1696,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1735,7 +1739,7 @@
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1745,7 +1749,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:14 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1775,19 +1779,19 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1797,12 +1801,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1812,23 +1816,23 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>JR2028350</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:17 UTC</t>
+          <t>2026-10-26 18:05 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1874,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1895,13 +1899,13 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>JR2028350</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1926,7 +1930,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:17 UTC</t>
+          <t>2026-10-26 18:07 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1941,7 +1945,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1957,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>SoC Software Engineer - New College Grad 2027</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1984,7 +1988,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>JR2026744</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1994,7 +1998,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2009,7 +2013,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:17 UTC</t>
+          <t>2026-10-26 18:07 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2024,29 +2028,29 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2061,13 +2065,13 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>R0249353</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2092,7 +2096,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25 15:18 UTC</t>
+          <t>2026-10-26 18:07 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2123,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Software Developer, Junior</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2129,7 +2133,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Aberdeen Proving Ground, MD</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2139,18 +2143,18 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0251954</t>
+          <t>R0252274</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Aberdeen-Proving-Ground-MD/Software-Developer--Junior_R0251954-1</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2175,7 +2179,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25 15:18 UTC</t>
+          <t>2026-10-26 18:09 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2190,7 +2194,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2206,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2227,58 +2231,224 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
+          <t>R0252273</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:09 UTC</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Model-Based Systems Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>R0249353</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:09 UTC</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>University, Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Fayetteville, NC</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
           <t>R0251802</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-25 15:18 UTC</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:09 UTC</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q21"/>
+  <autoFilter ref="A1:Q23"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2308,6 +2478,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,47 +580,47 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PhD Intern, Software Engineer - Graphics (2027)</t>
+          <t>Analyst, Early Career (Full Stack)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY</t>
+          <t>New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6219995004</t>
+          <t>8039471003</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/6219995004?gh_jid=6219995004</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,22 +645,22 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:04 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Supported</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+          <t>Current job posting states that visa sponsorship is unavailable.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -672,42 +672,42 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Analyst, Early Career (Full Stack)</t>
+          <t>Software Engineer I, Fullstack (Search)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>New York, New York, United States; San Francisco, California, United States</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8039471003</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,69 +732,69 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:04 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>Not Supported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Current job posting states that visa sponsorship is unavailable.</t>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:04 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:04 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,54 +921,54 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Jose, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>4722086006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:04 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,19 +1008,19 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Software Engineer III, GTOC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1030,32 +1030,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Redwood City, CA, United States</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8267895</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://job-boards.greenhouse.io/boxinc/jobs/8267895</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:05 UTC</t>
+          <t>2026-10-27 17:01 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:07 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Grad 2027</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1977,18 +1977,18 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>JR2026744</t>
+          <t>REF089878W</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Grad-2027_JR2026744</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:07 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2028,19 +2028,19 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SoC Software Engineer - New College Graduate 2026</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2060,18 +2060,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>JR2027552</t>
+          <t>REF089880W</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:07 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2111,19 +2111,19 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2148,13 +2148,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>R0252274</t>
+          <t>REF089882W</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:09 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2194,29 +2194,29 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>US - Bellevue, WA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2231,13 +2231,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>R0252273</t>
+          <t>REF089920W</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 18:09 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2277,29 +2277,29 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2309,18 +2309,18 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>R0249353</t>
+          <t>REF089919W</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 18:09 UTC</t>
+          <t>2026-10-27 17:03 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2360,19 +2360,19 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2397,58 +2397,1635 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
+          <t>REF089879W</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:03 UTC</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern - Foster City 2027</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>US - Foster City, CA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>REF089875W</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:03 UTC</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>US - Denver, CO</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>REF089779W</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:03 UTC</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Security Engineer</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>US - Ashburn, VA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>REF089778W</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:03 UTC</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern - 2027 Austin, TX</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>US - Austin, TX</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>REF089918W</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:03 UTC</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Bothell, Washington, United States</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>R-124488-3</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.att.jobs/job/bothell/ai-native-software-engineer-analyst-full-stack-python/117/102512395280</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:04 UTC</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Atlanta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>R-124488-2</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.att.jobs/job/atlanta/ai-native-software-engineer-analyst-full-stack-python/117/102512395232</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:04 UTC</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Alpharetta, Georgia, United States</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>R-124488-1</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.att.jobs/job/alpharetta/ai-native-software-engineer-analyst-full-stack-python/117/102512395168</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:04 UTC</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Dallas, Texas, United States</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>R-124488</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>company_career</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.att.jobs/job/dallas/ai-native-software-engineer-analyst-full-stack-python/117/102512395136</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:04 UTC</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>R0248060</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>R0252341</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>R0252340</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Dayton, OH</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>R0252345</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Dayton, OH</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>R0252342</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>R0252337</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>R0252335</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Lexington, MA</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>R0252274</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Lexington, MA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>R0252273</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Model-Based Systems Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>R0249353</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>University, Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Fayetteville, NC</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
           <t>R0251802</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>☐ Not Applied</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26 18:09 UTC</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:05 UTC</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q23"/>
+  <autoFilter ref="A1:Q42"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -2480,6 +4057,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8917377002</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8906750002</t>
+          <t>8917377002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Flexport</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Mercury Command</t>
+          <t>Software Engineer II, Autonomous Freight Technology</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>Bellevue, Washington, United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6233238004</t>
+          <t>8326088</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
+          <t>https://job-boards.greenhouse.io/flexport/jobs/8326088</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1530,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
+          <t>Software Engineer - Mercury Command</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,12 +1552,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1567,23 +1567,27 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>6233238004</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1598,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
+          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1656,7 +1660,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1666,7 +1670,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1681,7 +1685,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1728,18 +1732,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1749,7 +1753,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1779,7 +1783,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1811,7 +1815,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1822,7 +1826,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1832,7 +1836,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:01 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1862,19 +1866,19 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Agent Performance Modeling - New College Grad 2026</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1884,12 +1888,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>US, CA, Santa Clara</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1899,23 +1903,23 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2028350</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Agent-Performance-Modeling---New-College-Grad-2026_JR2028350</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1930,7 +1934,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1945,60 +1949,60 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
+          <t>Growth Engineer, Startups &amp; SMBs</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>New York, New York; New York, New York, United States</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>REF089878W</t>
+          <t>45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
+          <t>https://jobs.ashbyhq.com/notion/45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2013,7 +2017,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:37 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2028,7 +2032,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2050,7 +2054,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2071,7 +2075,7 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>REF089880W</t>
+          <t>REF089878W</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2096,7 +2100,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2111,7 +2115,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2127,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2133,7 +2137,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2154,7 +2158,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>REF089882W</t>
+          <t>REF089880W</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2164,7 +2168,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2179,7 +2183,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2194,7 +2198,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2210,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>US - Bellevue, WA</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2237,7 +2241,7 @@
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>REF089920W</t>
+          <t>REF089882W</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2262,7 +2266,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2277,7 +2281,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2293,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2299,7 +2303,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Bellevue, WA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2320,7 +2324,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>REF089919W</t>
+          <t>REF089920W</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2360,7 +2364,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2376,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2382,12 +2386,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2403,7 +2407,7 @@
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>REF089879W</t>
+          <t>REF089919W</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2413,7 +2417,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2428,7 +2432,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2443,7 +2447,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2459,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - Foster City 2027</t>
+          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2465,12 +2469,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2486,7 +2490,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>REF089875W</t>
+          <t>REF089879W</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2511,7 +2515,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2526,7 +2530,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2538,17 +2542,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
+          <t>Software Engineer, Intern - Foster City 2027</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2569,7 +2573,7 @@
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>REF089779W</t>
+          <t>REF089875W</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2579,7 +2583,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2594,7 +2598,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2609,7 +2613,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2625,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
+          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2631,7 +2635,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2652,7 +2656,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>REF089778W</t>
+          <t>REF089779W</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2662,7 +2666,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2692,7 +2696,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2704,17 +2708,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Austin, TX</t>
+          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2735,7 +2739,7 @@
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>REF089918W</t>
+          <t>REF089778W</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2745,7 +2749,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:03 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2775,19 +2779,19 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+          <t>Software Engineer, Intern - 2027 Austin, TX</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2797,17 +2801,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Bothell, Washington, United States</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2818,17 +2822,17 @@
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>R-124488-3</t>
+          <t>REF089918W</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/bothell/ai-native-software-engineer-analyst-full-stack-python/117/102512395280</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2843,7 +2847,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:04 UTC</t>
+          <t>2026-10-28 17:40 UTC</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2858,19 +2862,19 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2880,12 +2884,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2895,23 +2899,23 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>R-124488-2</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/atlanta/ai-native-software-engineer-analyst-full-stack-python/117/102512395232</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:04 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2941,60 +2945,60 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Alpharetta, Georgia, United States</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>R-124488-1</t>
+          <t>R0252341</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/alpharetta/ai-native-software-engineer-analyst-full-stack-python/117/102512395168</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:04 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3024,19 +3028,19 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>AI-Native Software Engineer Analyst, Full-Stack Python</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3046,38 +3050,38 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Dallas, Texas, United States</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>R-124488</t>
+          <t>R0252340</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>company_career</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://www.att.jobs/job/dallas/ai-native-software-engineer-analyst-full-stack-python/117/102512395136</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3092,7 +3096,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:04 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3123,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3129,7 +3133,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Dayton, OH</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3139,7 +3143,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3150,7 +3154,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>R0252345</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3175,7 +3179,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3190,7 +3194,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3206,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3212,7 +3216,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Dayton, OH</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3233,7 +3237,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>R0252341</t>
+          <t>R0252342</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3243,7 +3247,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3258,7 +3262,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3273,7 +3277,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3285,17 +3289,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3316,7 +3320,7 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>R0252340</t>
+          <t>R0252337</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3326,7 +3330,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3341,7 +3345,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3356,7 +3360,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3372,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3378,7 +3382,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3399,7 +3403,7 @@
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>R0252345</t>
+          <t>R0252335</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3409,7 +3413,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3439,7 +3443,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3455,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3482,7 +3486,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>R0252342</t>
+          <t>R0252274</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3492,7 +3496,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3507,7 +3511,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3522,7 +3526,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3538,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3544,7 +3548,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3565,7 +3569,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>R0252337</t>
+          <t>R0252273</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3575,7 +3579,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3590,7 +3594,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3605,7 +3609,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3617,17 +3621,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+          <t>Model-Based Systems Engineer, Junior</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3637,18 +3641,18 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>R0252335</t>
+          <t>R0249353</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3658,7 +3662,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3673,7 +3677,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3688,7 +3692,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3704,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+          <t>University, Software Engineer Intern</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3710,7 +3714,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>Fayetteville, NC</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3725,13 +3729,13 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>R0252274</t>
+          <t>R0251802</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3741,7 +3745,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3756,7 +3760,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 17:05 UTC</t>
+          <t>2026-10-28 17:41 UTC</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3771,261 +3775,12 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Lexington, MA</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>R0252273</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 17:05 UTC</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Model-Based Systems Engineer, Junior</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>R0249353</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-27 17:05 UTC</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>University, Software Engineer Intern</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Fayetteville, NC</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>R0251802</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27 17:05 UTC</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q42"/>
+  <autoFilter ref="A1:Q39"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -4073,9 +3828,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -580,27 +580,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Analyst, Early Career (Full Stack)</t>
+          <t>Software Engineer, Payments</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>New York, New York, United States; San Francisco, California, United States</t>
+          <t>Remote, USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -610,17 +610,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>8039471003</t>
+          <t>8332157</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
+          <t>https://careers.airbnb.com/positions/8332157?gh_jid=8332157</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -645,49 +645,49 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Not Supported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Current job posting states that visa sponsorship is unavailable.</t>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>PhD Intern, Security Engineer (2027)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>San Francisco, CA • New York, NY</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>6238015004</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://boards.greenhouse.io/figma/jobs/6238015004?gh_jid=6238015004</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,29 +747,29 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Analyst, Early Career (Full Stack)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, New York, United States; San Francisco, California, United States</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8039471003</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8039471003</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -819,69 +819,69 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Supported</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+          <t>Current job posting states that visa sponsorship is unavailable.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>Software Engineer I, Fullstack (Search)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Remote US</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>8017340003</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,54 +921,54 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering Intern [Winter 2027]</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Jose, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4722086006</t>
+          <t>8896654002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/figureai/jobs/4722086006</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,19 +1008,19 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer III, GTOC</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Redwood City, CA, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1045,17 +1045,17 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8267895</t>
+          <t>8896679002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/boxinc/jobs/8267895</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:37 UTC</t>
+          <t>2026-10-29 17:46 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:40 UTC</t>
+          <t>2026-10-29 17:49 UTC</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2894,18 +2894,18 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>R0252340</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2957,17 +2957,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Atlanta, GA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2982,13 +2982,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>R0252341</t>
+          <t>R0248138</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games-Software-Developer-Intern---Atlanta--GA_R0248138</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3065,13 +3065,13 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>R0252340</t>
+          <t>R0248404</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Software-Developer-Intern---Ft-Walton-Beach--FL_R0248404</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Charleston, SC</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3148,13 +3148,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>R0252345</t>
+          <t>R0248134</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Software-Developer-Intern_R0248134</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3206,17 +3206,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+          <t>University, 2027 Summer Games Software Developer Intern - Colorado Springs, CO</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>Colorado Springs, CO</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3231,13 +3231,13 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>R0252342</t>
+          <t>R0248130</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University--2027-Summer-Games-Software-Developer-Intern_R0248130</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3289,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3314,13 +3314,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>R0252337</t>
+          <t>R0248403</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Software-Developer-Intern---Annapolis-Junction--MD_R0248403</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Huntsville, AL</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3397,13 +3397,13 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>R0252335</t>
+          <t>R0248394</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Software-Developer-Intern---Huntsville--AL_R0248394</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Honolulu, HI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3480,13 +3480,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>R0252274</t>
+          <t>R0248393</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Software-Developer-Intern---Honolulu--HI_R0248393</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3538,17 +3538,17 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - El Segundo, CA</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3563,13 +3563,13 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>R0252273</t>
+          <t>R0248046</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Software-Developer-Intern---El-Segundo--CA_R0248046</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3621,17 +3621,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>University - 2027 Summer Games Software Developer Intern - San Diego, CA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3641,18 +3641,18 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>R0249353</t>
+          <t>R0248038</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Software-Developer-Intern---San-Diego--CA_R0248038</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3704,17 +3704,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>University, Software Engineer Intern</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Fayetteville, NC</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3729,13 +3729,13 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>R0251802</t>
+          <t>R0248388</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fayetteville-NC/University--Software-Engineer-Intern_R0251802</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Systems-Engineer-Intern---Ft-Walton-Beach--FL_R0248388</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 17:41 UTC</t>
+          <t>2026-10-29 17:51 UTC</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3775,12 +3775,1755 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
           <t>2026-10-28</t>
         </is>
       </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>R0248029</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Rome, NY</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>R0248386</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>University, 2027 Summer Games Software Developer Intern - Rome, NY</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Rome, NY</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>R0248141</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University--2027-Summer-Games-Software-Developer-Intern_R0248141</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Annapolis Junction, MD</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Annapolis Junction, MD</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>R0248384</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Systems-Engineer-Intern---Annapolis-Junction--MD_R0248384</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>R0248381</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games--Systems-Engineer-Intern---Atlanta--GA_R0248381</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Charleston, SC</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Charleston, SC</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>R0248369</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Systems-Engineer-Intern---Charleston--SC_R0248369</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Honolulu, HI</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Honolulu, HI</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>R0248370</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Systems-Engineer-Intern---Honolulu--HI_R0248370</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Colorado Springs, CO</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>R0248368</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University---2027-Summer-Games-Systems-Engineer-Intern---Colorado-Springs--CO_R0248368</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>R0248366</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Systems-Engineer-Intern---El-Segundo--CA_R0248366</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - San Diego, CA</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>R0248365</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Systems-Engineer-Intern---San-Diego--CA_R0248365</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Huntsville, AL</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Huntsville, AL</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>R0249188</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Systems-Engineer-Intern---Huntsville--AL_R0249188</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - McLean, VA</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>R0248361</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University---2027-Summer-Games-Systems-Engineer-Intern---McLean--VA_R0248361</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Dayton, OH</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>R0252345</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Dayton, OH</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>R0252342</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>R0252341</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>R0252337</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>R0252335</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Lexington, MA</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>R0252274</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Lexington, MA</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>R0252273</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>McLean, VA</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>R0248060</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Model-Based Systems Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>R0249353</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:51 UTC</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q39"/>
+  <autoFilter ref="A1:Q60"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -3828,6 +5571,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:26 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:26 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:26 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,19 +834,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I, Fullstack (Search)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Remote US</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8017340003</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/affirm/jobs/8017340003</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,34 +921,34 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8896654002</t>
+          <t>8917377002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896654002?gh_jid=8896654002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,26 +1008,26 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>San Francisco, CA</t>
@@ -1035,27 +1035,27 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8896679002</t>
+          <t>8886748002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8896679002?gh_jid=8896679002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8906750002</t>
+          <t>8886605002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,19 +1182,19 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Flexport</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer II, Autonomous Freight Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Bellevue, Washington, United States</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8917377002</t>
+          <t>8326088</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
+          <t>https://job-boards.greenhouse.io/flexport/jobs/8326088</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
+          <t>Software Engineer - Mercury Command</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8886748002</t>
+          <t>6233238004</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
+          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,17 +1378,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1396,24 +1396,20 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>8886605002</t>
+          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
+          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1428,7 +1424,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1443,19 +1439,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Flexport</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer II, Autonomous Freight Technology</t>
+          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1465,12 +1461,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bellevue, Washington, United States</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1480,27 +1476,23 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8326088</t>
+          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/flexport/jobs/8326088</t>
+          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1515,7 +1507,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1530,19 +1522,19 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Mercury Command</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1552,42 +1544,38 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>6233238004</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1602,7 +1590,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1617,7 +1605,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1617,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1654,13 +1642,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1670,7 +1658,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1685,7 +1673,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1700,29 +1688,29 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
+          <t>Growth Engineer, Startups &amp; SMBs</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>New York, New York; New York, New York, United States</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1737,23 +1725,23 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>https://jobs.ashbyhq.com/notion/45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1768,7 +1756,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:27 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1783,19 +1771,19 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>AI Systems Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1805,12 +1793,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>US, TX, Austin</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1820,23 +1808,23 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>JR2027170</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-TX-Austin/AI-Systems-Software-Engineering-Intern---Summer-2027_JR2027170</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1851,7 +1839,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:29 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1866,19 +1854,19 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Compiler Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1888,38 +1876,38 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>US, WA, Redmond</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>JR2028607</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-WA-Redmond/Compiler-Software-Engineering-Intern---Summer-2027_JR2028607</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1934,7 +1922,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:29 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1949,60 +1937,60 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Growth Engineer, Startups &amp; SMBs</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>New York, New York; New York, New York, United States</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45f60d0e-e44f-40c5-985e-4096a8966860</t>
+          <t>REF089878W</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/45f60d0e-e44f-40c5-985e-4096a8966860</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2017,7 +2005,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:46 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2032,7 +2020,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2032,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2054,7 +2042,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2075,7 +2063,7 @@
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>REF089878W</t>
+          <t>REF089880W</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2085,7 +2073,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2100,7 +2088,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2115,7 +2103,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2115,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2137,7 +2125,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2158,7 +2146,7 @@
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>REF089880W</t>
+          <t>REF089882W</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2168,7 +2156,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2183,7 +2171,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2198,7 +2186,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2198,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2220,7 +2208,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>US - Bellevue, WA</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2241,7 +2229,7 @@
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>REF089882W</t>
+          <t>REF089920W</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2251,7 +2239,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2266,7 +2254,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2281,7 +2269,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2281,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2303,7 +2291,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>US - Bellevue, WA</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2324,7 +2312,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>REF089920W</t>
+          <t>REF089919W</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2334,7 +2322,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2349,7 +2337,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2364,7 +2352,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2364,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
+          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2386,12 +2374,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2407,7 +2395,7 @@
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>REF089919W</t>
+          <t>REF089879W</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2417,7 +2405,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2432,7 +2420,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2447,7 +2435,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2447,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
+          <t>Software Engineer, Intern - Foster City 2027</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2469,12 +2457,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2490,7 +2478,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>REF089879W</t>
+          <t>REF089875W</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2500,7 +2488,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2515,7 +2503,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2530,7 +2518,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2542,17 +2530,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - Foster City 2027</t>
+          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2573,7 +2561,7 @@
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>REF089875W</t>
+          <t>REF089779W</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2583,7 +2571,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2598,7 +2586,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2613,7 +2601,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2613,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
+          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2635,7 +2623,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2656,7 +2644,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>REF089779W</t>
+          <t>REF089778W</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2666,7 +2654,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2681,7 +2669,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2696,7 +2684,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2696,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
+          <t>Software Engineer, Intern - 2027 Austin, TX</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2739,7 +2727,7 @@
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>REF089778W</t>
+          <t>REF089918W</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2749,7 +2737,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2764,7 +2752,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:30 UTC</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2779,19 +2767,19 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Austin, TX</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2801,7 +2789,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2816,13 +2804,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>REF089918W</t>
+          <t>R0252340</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2832,7 +2820,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2847,7 +2835,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:49 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2862,7 +2850,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2862,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Atlanta, GA</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2884,7 +2872,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2905,7 +2893,7 @@
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>R0252340</t>
+          <t>R0248138</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2915,7 +2903,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games-Software-Developer-Intern---Atlanta--GA_R0248138</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2930,7 +2918,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2945,7 +2933,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2945,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Atlanta, GA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2967,7 +2955,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2988,7 +2976,7 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>R0248138</t>
+          <t>R0248404</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2998,7 +2986,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games-Software-Developer-Intern---Atlanta--GA_R0248138</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Software-Developer-Intern---Ft-Walton-Beach--FL_R0248404</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3013,7 +3001,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3028,7 +3016,7 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3028,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Ft. Walton Beach, FL</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Charleston, SC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3050,7 +3038,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3071,7 +3059,7 @@
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>R0248404</t>
+          <t>R0248134</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -3081,7 +3069,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Software-Developer-Intern---Ft-Walton-Beach--FL_R0248404</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Software-Developer-Intern_R0248134</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3096,7 +3084,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3111,7 +3099,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3111,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Charleston, SC</t>
+          <t>University, 2027 Summer Games Software Developer Intern - Colorado Springs, CO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3133,7 +3121,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Colorado Springs, CO</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3154,7 +3142,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>R0248134</t>
+          <t>R0248130</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3164,7 +3152,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Software-Developer-Intern_R0248134</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University--2027-Summer-Games-Software-Developer-Intern_R0248130</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3179,7 +3167,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3194,7 +3182,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3194,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - Colorado Springs, CO</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3216,7 +3204,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO</t>
+          <t>Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3237,7 +3225,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>R0248130</t>
+          <t>R0248403</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3247,7 +3235,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University--2027-Summer-Games-Software-Developer-Intern_R0248130</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Software-Developer-Intern---Annapolis-Junction--MD_R0248403</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3262,7 +3250,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3277,7 +3265,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3277,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Annapolis Junction, MD</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Huntsville, AL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3299,7 +3287,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3320,7 +3308,7 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>R0248403</t>
+          <t>R0248394</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3330,7 +3318,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Software-Developer-Intern---Annapolis-Junction--MD_R0248403</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Software-Developer-Intern---Huntsville--AL_R0248394</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3345,7 +3333,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3360,7 +3348,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3360,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Huntsville, AL</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Honolulu, HI</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3382,7 +3370,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3403,7 +3391,7 @@
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>R0248394</t>
+          <t>R0248393</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3413,7 +3401,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Software-Developer-Intern---Huntsville--AL_R0248394</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Software-Developer-Intern---Honolulu--HI_R0248393</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3428,7 +3416,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3443,7 +3431,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3443,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Honolulu, HI</t>
+          <t>University - 2027 Summer Games Software Developer Intern - El Segundo, CA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3465,7 +3453,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3486,7 +3474,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>R0248393</t>
+          <t>R0248046</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3496,7 +3484,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Software-Developer-Intern---Honolulu--HI_R0248393</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Software-Developer-Intern---El-Segundo--CA_R0248046</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3511,7 +3499,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3526,7 +3514,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3526,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - El Segundo, CA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - San Diego, CA</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3548,7 +3536,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3569,7 +3557,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>R0248046</t>
+          <t>R0248038</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3579,7 +3567,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Software-Developer-Intern---El-Segundo--CA_R0248046</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Software-Developer-Intern---San-Diego--CA_R0248038</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3594,7 +3582,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3609,7 +3597,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3621,17 +3609,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - San Diego, CA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3652,7 +3640,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>R0248038</t>
+          <t>R0248388</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3662,7 +3650,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Software-Developer-Intern---San-Diego--CA_R0248038</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Systems-Engineer-Intern---Ft-Walton-Beach--FL_R0248388</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3677,7 +3665,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3692,7 +3680,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3704,17 +3692,17 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Ft. Walton Beach, FL</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3735,7 +3723,7 @@
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>R0248388</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3745,7 +3733,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Systems-Engineer-Intern---Ft-Walton-Beach--FL_R0248388</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3760,7 +3748,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3775,7 +3763,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3787,17 +3775,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3818,7 +3806,7 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>R0248029</t>
+          <t>R0248386</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3828,7 +3816,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3843,7 +3831,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3858,7 +3846,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3858,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
+          <t>University, 2027 Summer Games Software Developer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -3901,7 +3889,7 @@
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>R0248386</t>
+          <t>R0248141</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3911,7 +3899,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University--2027-Summer-Games-Software-Developer-Intern_R0248141</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3926,7 +3914,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3941,7 +3929,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3953,17 +3941,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - Rome, NY</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Rome, NY</t>
+          <t>Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3984,7 +3972,7 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>R0248141</t>
+          <t>R0248384</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3994,7 +3982,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University--2027-Summer-Games-Software-Developer-Intern_R0248141</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Systems-Engineer-Intern---Annapolis-Junction--MD_R0248384</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4009,7 +3997,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -4024,7 +4012,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4024,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Annapolis Junction, MD</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Atlanta, GA</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4046,7 +4034,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4067,7 +4055,7 @@
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>R0248384</t>
+          <t>R0248381</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -4077,7 +4065,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Systems-Engineer-Intern---Annapolis-Junction--MD_R0248384</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games--Systems-Engineer-Intern---Atlanta--GA_R0248381</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4092,7 +4080,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -4107,7 +4095,7 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4107,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Atlanta, GA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Charleston, SC</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4129,7 +4117,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4150,7 +4138,7 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>R0248381</t>
+          <t>R0248369</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4160,7 +4148,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games--Systems-Engineer-Intern---Atlanta--GA_R0248381</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Systems-Engineer-Intern---Charleston--SC_R0248369</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4175,7 +4163,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4190,7 +4178,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4190,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Charleston, SC</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Honolulu, HI</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4212,7 +4200,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4233,7 +4221,7 @@
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>R0248369</t>
+          <t>R0248370</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -4243,7 +4231,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Systems-Engineer-Intern---Charleston--SC_R0248369</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Systems-Engineer-Intern---Honolulu--HI_R0248370</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4258,7 +4246,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -4273,7 +4261,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4273,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Honolulu, HI</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Colorado Springs, CO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4295,7 +4283,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Colorado Springs, CO</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4316,7 +4304,7 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>R0248370</t>
+          <t>R0248368</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4326,7 +4314,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Systems-Engineer-Intern---Honolulu--HI_R0248370</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University---2027-Summer-Games-Systems-Engineer-Intern---Colorado-Springs--CO_R0248368</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4341,7 +4329,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4356,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Colorado Springs, CO</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - El Segundo, CA</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4378,7 +4366,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4399,7 +4387,7 @@
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>R0248368</t>
+          <t>R0248366</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -4409,7 +4397,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University---2027-Summer-Games-Systems-Engineer-Intern---Colorado-Springs--CO_R0248368</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Systems-Engineer-Intern---El-Segundo--CA_R0248366</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4424,7 +4412,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4439,7 +4427,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4439,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - El Segundo, CA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - San Diego, CA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4461,7 +4449,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4482,7 +4470,7 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>R0248366</t>
+          <t>R0248365</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4492,7 +4480,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Systems-Engineer-Intern---El-Segundo--CA_R0248366</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Systems-Engineer-Intern---San-Diego--CA_R0248365</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4507,7 +4495,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -4522,7 +4510,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4522,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - San Diego, CA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Huntsville, AL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4544,7 +4532,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4565,7 +4553,7 @@
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>R0248365</t>
+          <t>R0249188</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -4575,7 +4563,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Systems-Engineer-Intern---San-Diego--CA_R0248365</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Systems-Engineer-Intern---Huntsville--AL_R0249188</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4590,7 +4578,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4605,7 +4593,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4605,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Huntsville, AL</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4627,7 +4615,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4648,7 +4636,7 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>R0249188</t>
+          <t>R0248361</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4658,7 +4646,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Systems-Engineer-Intern---Huntsville--AL_R0249188</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University---2027-Summer-Games-Systems-Engineer-Intern---McLean--VA_R0248361</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4673,7 +4661,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4688,7 +4676,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4688,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - McLean, VA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Dayton, OH</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4731,7 +4719,7 @@
       <c r="H51" s="4" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>R0248361</t>
+          <t>R0252345</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -4741,7 +4729,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University---2027-Summer-Games-Systems-Engineer-Intern---McLean--VA_R0248361</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4756,7 +4744,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4771,7 +4759,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4771,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4814,7 +4802,7 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>R0252345</t>
+          <t>R0252342</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4824,7 +4812,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4839,7 +4827,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4854,7 +4842,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4854,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4876,7 +4864,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4897,7 +4885,7 @@
       <c r="H53" s="4" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>R0252342</t>
+          <t>R0252341</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4907,7 +4895,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4922,7 +4910,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4937,7 +4925,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4937,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4959,7 +4947,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4980,7 +4968,7 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>R0252341</t>
+          <t>R0252337</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4990,7 +4978,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5005,7 +4993,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -5020,7 +5008,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5020,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5063,7 +5051,7 @@
       <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>R0252337</t>
+          <t>R0252335</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -5073,7 +5061,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5088,7 +5076,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -5103,7 +5091,7 @@
       </c>
       <c r="Q55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5103,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5125,7 +5113,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5146,7 +5134,7 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>R0252335</t>
+          <t>R0252274</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -5156,7 +5144,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5171,7 +5159,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -5186,7 +5174,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5186,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5229,7 +5217,7 @@
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>R0252274</t>
+          <t>R0252273</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -5239,7 +5227,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5254,7 +5242,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5269,7 +5257,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5281,17 +5269,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5301,18 +5289,18 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>R0252273</t>
+          <t>R0248060</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -5322,7 +5310,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5337,7 +5325,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5352,7 +5340,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5364,17 +5352,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>Model-Based Systems Engineer, Junior</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5389,13 +5377,13 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>R0249353</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -5405,7 +5393,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5420,7 +5408,7 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 17:51 UTC</t>
+          <t>2026-10-30 17:31 UTC</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
@@ -5435,95 +5423,12 @@
       </c>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Model-Based Systems Engineer, Junior</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>El Segundo, CA</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>R0249353</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>workday</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29 17:51 UTC</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q60"/>
+  <autoFilter ref="A1:Q59"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -5591,7 +5496,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/current/jobs.xlsx
+++ b/data/current/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$Q$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:26 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:26 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:26 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -834,19 +834,19 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer, Jade - AI Financial Partner</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>8906750002</t>
+          <t>8868948002</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8868948002?gh_jid=8868948002</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -921,19 +921,19 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Software Engineer, Membership Experience</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8917377002</t>
+          <t>8922481002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8922481002?gh_jid=8922481002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1030,32 +1030,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>8886748002</t>
+          <t>8906750002</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8906750002</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1127,22 +1127,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8886605002</t>
+          <t>8917377002</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8917377002</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1182,19 +1182,19 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Flexport</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer II, Autonomous Freight Technology</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Spring 2028)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1204,32 +1204,32 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Bellevue, Washington, United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>8326088</t>
+          <t>8886748002</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/flexport/jobs/8326088</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886748002</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1269,19 +1269,19 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer - Mercury Command</t>
+          <t>Undergrad Software Engineering Intern (Grad Year: Winter 2027)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6233238004</t>
+          <t>8886605002</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8886605002</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1356,19 +1356,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Flexport</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
+          <t>Software Engineer II, Autonomous Freight Technology</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Bellevue, Washington, United States</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1393,23 +1393,27 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>8326088</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
+          <t>https://job-boards.greenhouse.io/flexport/jobs/8326088</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1424,7 +1428,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1439,19 +1443,19 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
+          <t>Software Engineer - Mercury Command</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1461,12 +1465,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA, New York, NY, Portland, OR, or Remote within Canada or United States</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1476,23 +1480,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>6233238004</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
+          <t>https://job-boards.greenhouse.io/mercury/jobs/6233238004</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1507,7 +1515,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1522,7 +1530,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1542,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Internship - Query Engines</t>
+          <t>Forward Deployed Software Engineer, Internship - Warp Speed</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1554,18 +1562,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1575,7 +1583,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
+          <t>https://jobs.lever.co/palantir/b3d81928-6c26-432f-8a0a-36602c2eefcb</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1590,7 +1598,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1605,7 +1613,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1625,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad - Query Engines</t>
+          <t>Forward Deployed Software Engineer, New Grad - Warp Speed</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1642,13 +1650,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1658,7 +1666,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
+          <t>https://jobs.lever.co/palantir/66b495eb-aaf9-4bf9-a759-41854534add7</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1673,7 +1681,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1688,29 +1696,29 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Growth Engineer, Startups &amp; SMBs</t>
+          <t>Software Engineer, Internship - Query Engines</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>New York, New York; New York, New York, United States</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1720,28 +1728,28 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>45f60d0e-e44f-40c5-985e-4096a8966860</t>
+          <t>da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/notion/45f60d0e-e44f-40c5-985e-4096a8966860</t>
+          <t>https://jobs.lever.co/palantir/da774f81-c98c-4dcf-9b9c-949fd7d90a13</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1756,7 +1764,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:27 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1771,19 +1779,19 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AI Systems Software Engineering Intern - Summer 2027</t>
+          <t>Software Engineer, New Grad - Query Engines</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1793,38 +1801,38 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>US, TX, Austin</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>JR2027170</t>
+          <t>90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-TX-Austin/AI-Systems-Software-Engineering-Intern---Summer-2027_JR2027170</t>
+          <t>https://jobs.lever.co/palantir/90329118-d9b7-4b96-acdf-13377e3196ac</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1839,7 +1847,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:29 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1854,60 +1862,60 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Compiler Software Engineering Intern - Summer 2027</t>
+          <t>Growth Engineer, Startups &amp; SMBs</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>US, WA, Redmond</t>
+          <t>New York, New York; New York, New York, United States</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>JR2028607</t>
+          <t>45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-WA-Redmond/Compiler-Software-Engineering-Intern---Summer-2027_JR2028607</t>
+          <t>https://jobs.ashbyhq.com/notion/45f60d0e-e44f-40c5-985e-4096a8966860</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1922,7 +1930,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:29 UTC</t>
+          <t>2026-10-31 16:30 UTC</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1937,19 +1945,19 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
+          <t>Compiler Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1959,7 +1967,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US, WA, Redmond</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1974,13 +1982,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>REF089878W</t>
+          <t>JR2028607</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1990,7 +1998,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-WA-Redmond/Compiler-Software-Engineering-Intern---Summer-2027_JR2028607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2005,7 +2013,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2020,19 +2028,19 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
+          <t>SoC Software Engineer - New College Graduate 2026</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2042,7 +2050,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2052,18 +2060,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>REF089880W</t>
+          <t>JR2027552</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2073,7 +2081,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/SoC-Software-Engineer---New-College-Graduate-2026_JR2027552-1</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -2103,19 +2111,19 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
+          <t>Software Engineer, Hardware Tools and Methodology - New College Grad 2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2125,7 +2133,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>US, CA, Santa Clara</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2135,18 +2143,18 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>REF089882W</t>
+          <t>JR2018659</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-CA-Santa-Clara/Software-Engineer--Hardware-Tools-and-Methodology---New-College-Grad-2026_JR2018659</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2171,7 +2179,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2186,19 +2194,19 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
+          <t>AI Systems Software Engineering Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2208,7 +2216,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>US - Bellevue, WA</t>
+          <t>US, TX, Austin</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2223,13 +2231,13 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>REF089920W</t>
+          <t>JR2027170</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -2239,7 +2247,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
+          <t>https://nvidia.wd5.myworkdayjobs.com/NVIDIAExternalCareerSite/job/US-TX-Austin/AI-Systems-Software-Engineering-Intern---Summer-2027_JR2027170</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2254,7 +2262,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
@@ -2269,7 +2277,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2289,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Ashburn</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2291,7 +2299,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2312,7 +2320,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>REF089919W</t>
+          <t>REF089878W</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2322,7 +2330,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Ashburn_REF089878W-1</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2337,7 +2345,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2352,7 +2360,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2372,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Highlands Ranch</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2374,12 +2382,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2395,7 +2403,7 @@
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>REF089879W</t>
+          <t>REF089880W</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2405,7 +2413,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Highlands-Ranch_REF089880W-1</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2420,7 +2428,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
@@ -2435,7 +2443,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2455,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - Foster City 2027</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Austin, TX - 2027</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2457,7 +2465,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>US - Foster City, CA</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2478,7 +2486,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>REF089875W</t>
+          <t>REF089882W</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Austin--TX---2027_REF089882W-1</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2503,7 +2511,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2518,7 +2526,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2530,17 +2538,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Bellevue</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>US - Denver, CO</t>
+          <t>US - Bellevue, WA</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2561,7 +2569,7 @@
       <c r="H25" s="4" t="inlineStr"/>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>REF089779W</t>
+          <t>REF089920W</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2571,7 +2579,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Bellevue-WA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Bellevue_REF089920W-2</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2586,7 +2594,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
@@ -2601,7 +2609,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2621,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
+          <t>2027 Sophomore Internship Program - Software Engineer Intern, Foster City</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>US - Ashburn, VA</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2644,7 +2652,7 @@
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>REF089778W</t>
+          <t>REF089919W</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2654,7 +2662,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/XMLNAME-2027-Sophomore-Internship-Program---Software-Engineer-Intern--Foster-City_REF089919W-1</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2669,7 +2677,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2684,7 +2692,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2704,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Austin, TX</t>
+          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2706,12 +2714,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>US - Austin, TX</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2727,7 +2735,7 @@
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>REF089918W</t>
+          <t>REF089879W</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2737,7 +2745,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Software-Engineer--Intern---2027-Ashburn--VA_REF089879W-1</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2752,7 +2760,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:30 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
@@ -2767,19 +2775,19 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
+          <t>Software Engineer, Intern - Foster City 2027</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2789,7 +2797,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>US - Foster City, CA</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2804,13 +2812,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>R0252340</t>
+          <t>REF089875W</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2820,7 +2828,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Foster-City-CA/Software-Engineer--Intern---Foster-City-2027_REF089875W-1</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2850,29 +2858,29 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Atlanta, GA</t>
+          <t>Network and Security Engineering Intern - 2027, Highlands Ranch, CO</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>US - Denver, CO</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2887,13 +2895,13 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>R0248138</t>
+          <t>REF089779W</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2903,7 +2911,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games-Software-Developer-Intern---Atlanta--GA_R0248138</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Denver-CO/Network-and-Security-Engineering-Intern---2027--Highlands-Ranch--CO_REF089779W-1</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2918,7 +2926,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -2933,29 +2941,29 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Ft. Walton Beach, FL</t>
+          <t>Network and Security Engineering Intern - 2027, Ashburn, VA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Security Engineer</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL</t>
+          <t>US - Ashburn, VA</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2970,13 +2978,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>R0248404</t>
+          <t>REF089778W</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2986,7 +2994,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Software-Developer-Intern---Ft-Walton-Beach--FL_R0248404</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Ashburn-VA/Network-and-Security-Engineering-Intern---2027--Ashburn--VA_REF089778W</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3001,7 +3009,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3016,19 +3024,19 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Charleston, SC</t>
+          <t>Software Engineer, Intern - 2027 Austin, TX</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3038,7 +3046,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>US - Austin, TX</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3053,13 +3061,13 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>R0248134</t>
+          <t>REF089918W</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -3069,7 +3077,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Software-Developer-Intern_R0248134</t>
+          <t>https://visa.wd5.myworkdayjobs.com/Visa/job/US---Austin-TX/Software-Engineer--Intern---2027-Austin--TX_REF089918W-1</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3084,7 +3092,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:32 UTC</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -3099,7 +3107,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3119,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - Colorado Springs, CO</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3121,7 +3129,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3142,7 +3150,7 @@
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>R0248130</t>
+          <t>R0252340</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3152,7 +3160,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University--2027-Summer-Games-Software-Developer-Intern_R0248130</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games-Software-Developer-Intern---Royal-Oaks--MI_R0252340</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3167,7 +3175,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3182,7 +3190,7 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3202,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Annapolis Junction, MD</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Atlanta, GA</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3204,7 +3212,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3225,7 +3233,7 @@
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>R0248403</t>
+          <t>R0248138</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3235,7 +3243,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Software-Developer-Intern---Annapolis-Junction--MD_R0248403</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games-Software-Developer-Intern---Atlanta--GA_R0248138</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -3265,7 +3273,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3285,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Huntsville, AL</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3287,7 +3295,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3308,7 +3316,7 @@
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>R0248394</t>
+          <t>R0248404</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3318,7 +3326,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Software-Developer-Intern---Huntsville--AL_R0248394</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Software-Developer-Intern---Ft-Walton-Beach--FL_R0248404</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3333,7 +3341,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3348,7 +3356,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3368,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Honolulu, HI</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Charleston, SC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -3370,7 +3378,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3391,7 +3399,7 @@
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>R0248393</t>
+          <t>R0248134</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -3401,7 +3409,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Software-Developer-Intern---Honolulu--HI_R0248393</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Software-Developer-Intern_R0248134</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3416,7 +3424,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3431,7 +3439,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3451,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - El Segundo, CA</t>
+          <t>University, 2027 Summer Games Software Developer Intern - Colorado Springs, CO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3453,7 +3461,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Colorado Springs, CO</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3474,7 +3482,7 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>R0248046</t>
+          <t>R0248130</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3484,7 +3492,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Software-Developer-Intern---El-Segundo--CA_R0248046</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University--2027-Summer-Games-Software-Developer-Intern_R0248130</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3499,7 +3507,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3514,7 +3522,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3534,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - San Diego, CA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3536,7 +3544,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Annapolis Junction, MD</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3557,7 +3565,7 @@
       <c r="H37" s="4" t="inlineStr"/>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>R0248038</t>
+          <t>R0248403</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3567,7 +3575,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Software-Developer-Intern---San-Diego--CA_R0248038</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Software-Developer-Intern---Annapolis-Junction--MD_R0248403</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3582,7 +3590,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -3597,7 +3605,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3609,17 +3617,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Ft. Walton Beach, FL</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Huntsville, AL</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Fort Walton Beach, FL</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3640,7 +3648,7 @@
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>R0248388</t>
+          <t>R0248394</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -3650,7 +3658,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Systems-Engineer-Intern---Ft-Walton-Beach--FL_R0248388</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Software-Developer-Intern---Huntsville--AL_R0248394</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3665,7 +3673,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3680,7 +3688,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3700,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Honolulu, HI</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3702,7 +3710,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3723,7 +3731,7 @@
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>R0248029</t>
+          <t>R0248393</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -3733,7 +3741,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Software-Developer-Intern---Honolulu--HI_R0248393</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3748,7 +3756,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
@@ -3763,7 +3771,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3783,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Rome, NY</t>
+          <t>University - 2027 Summer Games Software Developer Intern - El Segundo, CA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Rome, NY</t>
+          <t>El Segundo, CA</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3806,7 +3814,7 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>R0248386</t>
+          <t>R0248046</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3816,7 +3824,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University---2027-Summer-Games-Systems-Engineer-Intern---Rome--NY_R0248386</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Software-Developer-Intern---El-Segundo--CA_R0248046</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3831,7 +3839,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3846,7 +3854,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3866,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>University, 2027 Summer Games Software Developer Intern - Rome, NY</t>
+          <t>University - 2027 Summer Games Software Developer Intern - San Diego, CA</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3868,7 +3876,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Rome, NY</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3889,7 +3897,7 @@
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>R0248141</t>
+          <t>R0248038</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -3899,7 +3907,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University--2027-Summer-Games-Software-Developer-Intern_R0248141</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Software-Developer-Intern---San-Diego--CA_R0248038</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3914,7 +3922,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3929,7 +3937,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3949,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Annapolis Junction, MD</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Ft. Walton Beach, FL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3951,7 +3959,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD</t>
+          <t>Fort Walton Beach, FL</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3972,7 +3980,7 @@
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>R0248384</t>
+          <t>R0248388</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3982,7 +3990,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Annapolis-Junction-MD/University---2027-Summer-Games-Systems-Engineer-Intern---Annapolis-Junction--MD_R0248384</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Fort-Walton-Beach-FL/University---2027-Summer-Games-Systems-Engineer-Intern---Ft-Walton-Beach--FL_R0248388</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3997,7 +4005,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -4012,7 +4020,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4024,17 +4032,17 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Atlanta, GA</t>
+          <t>University, 2027 Summer Games Software Developer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4055,7 +4063,7 @@
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>R0248381</t>
+          <t>R0248029</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -4065,7 +4073,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games--Systems-Engineer-Intern---Atlanta--GA_R0248381</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University--2027-Summer-Games-Software-Developer-Intern_R0248029</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
@@ -4095,7 +4103,7 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4107,17 +4115,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Charleston, SC</t>
+          <t>University, 2027 Summer Games Software Developer Intern - Rome, NY</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Charleston, SC</t>
+          <t>Rome, NY</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4138,7 +4146,7 @@
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>R0248369</t>
+          <t>R0248141</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -4148,7 +4156,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Systems-Engineer-Intern---Charleston--SC_R0248369</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Rome-NY/University--2027-Summer-Games-Software-Developer-Intern_R0248141</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4163,7 +4171,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4178,7 +4186,7 @@
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4198,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Honolulu, HI</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Atlanta, GA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -4200,7 +4208,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Honolulu, HI</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4221,7 +4229,7 @@
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>R0248370</t>
+          <t>R0248381</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -4231,7 +4239,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Systems-Engineer-Intern---Honolulu--HI_R0248370</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Atlanta-GA/University---2027-Summer-Games--Systems-Engineer-Intern---Atlanta--GA_R0248381</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4246,7 +4254,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
@@ -4261,7 +4269,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4281,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Colorado Springs, CO</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Charleston, SC</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4283,7 +4291,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO</t>
+          <t>Charleston, SC</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4304,7 +4312,7 @@
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>R0248368</t>
+          <t>R0248369</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4314,7 +4322,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University---2027-Summer-Games-Systems-Engineer-Intern---Colorado-Springs--CO_R0248368</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Charleston-SC/University---2027-Summer-Games-Systems-Engineer-Intern---Charleston--SC_R0248369</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4329,7 +4337,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -4344,7 +4352,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4364,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - El Segundo, CA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Honolulu, HI</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -4366,7 +4374,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>Honolulu, HI</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4387,7 +4395,7 @@
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>R0248366</t>
+          <t>R0248370</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -4397,7 +4405,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/University---2027-Summer-Games-Systems-Engineer-Intern---El-Segundo--CA_R0248366</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Honolulu-HI/University---2027-Summer-Games-Systems-Engineer-Intern---Honolulu--HI_R0248370</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4412,7 +4420,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
@@ -4427,7 +4435,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4447,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - San Diego, CA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Colorado Springs, CO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4449,7 +4457,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>San Diego, CA</t>
+          <t>Colorado Springs, CO</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4470,7 +4478,7 @@
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>R0248365</t>
+          <t>R0248368</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4480,7 +4488,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Systems-Engineer-Intern---San-Diego--CA_R0248365</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Colorado-Springs-CO/University---2027-Summer-Games-Systems-Engineer-Intern---Colorado-Springs--CO_R0248368</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4495,7 +4503,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -4510,7 +4518,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4530,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Huntsville, AL</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - San Diego, CA</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -4532,7 +4540,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Huntsville, AL</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4553,7 +4561,7 @@
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>R0249188</t>
+          <t>R0248365</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -4563,7 +4571,7 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Systems-Engineer-Intern---Huntsville--AL_R0249188</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/San-Diego-CA/University---2027-Summer-Games-Systems-Engineer-Intern---San-Diego--CA_R0248365</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4578,7 +4586,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
@@ -4593,7 +4601,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4613,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - McLean, VA</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Huntsville, AL</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4615,7 +4623,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Huntsville, AL</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4636,7 +4644,7 @@
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>R0248361</t>
+          <t>R0249188</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4646,7 +4654,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University---2027-Summer-Games-Systems-Engineer-Intern---McLean--VA_R0248361</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Huntsville-AL/University---2027-Summer-Games-Systems-Engineer-Intern---Huntsville--AL_R0249188</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4661,7 +4669,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4676,7 +4684,7 @@
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4696,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - McLean, VA</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Dayton, OH</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4719,7 +4727,7 @@
       <c r="H51" s="4" t="inlineStr"/>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>R0252345</t>
+          <t>R0248361</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -4729,7 +4737,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/University---2027-Summer-Games-Systems-Engineer-Intern---McLean--VA_R0248361</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4744,7 +4752,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
@@ -4759,7 +4767,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4779,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4802,7 +4810,7 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>R0252342</t>
+          <t>R0252345</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4812,7 +4820,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games-Software-Developer-Intern---Dayton--OH_R0252345</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4827,7 +4835,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4842,7 +4850,7 @@
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4862,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Dayton, OH</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4864,7 +4872,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Detroit, MI</t>
+          <t>Dayton, OH</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4885,7 +4893,7 @@
       <c r="H53" s="4" t="inlineStr"/>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>R0252341</t>
+          <t>R0252342</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -4895,7 +4903,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Dayton-OH/University---2027-Summer-Games--Systems-Engineer-Intern---Dayton--OH_R0252342</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4910,7 +4918,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -4925,7 +4933,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4945,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Royal Oaks, MI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4947,7 +4955,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Albuquerque, NM</t>
+          <t>Detroit, MI</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4968,7 +4976,7 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>R0252337</t>
+          <t>R0252341</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4978,7 +4986,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Detroit-MI/University---2027-Summer-Games--Systems-Engineer-Intern---Royal-Oaks--MI_R0252341</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4993,7 +5001,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -5008,7 +5016,7 @@
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5028,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
+          <t>University - 2027 Summer Games, Systems Engineer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5051,7 +5059,7 @@
       <c r="H55" s="4" t="inlineStr"/>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>R0252335</t>
+          <t>R0252337</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -5061,7 +5069,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games--Systems-Engineer-Intern---Albuquerque--NM_R0252337</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5076,7 +5084,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
@@ -5091,7 +5099,7 @@
       </c>
       <c r="Q55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5111,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Albuquerque, NM</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5113,7 +5121,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Lexington, MA</t>
+          <t>Albuquerque, NM</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5134,7 +5142,7 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>R0252274</t>
+          <t>R0252335</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -5144,7 +5152,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Albuquerque-NM/University---2027-Summer-Games-Software-Developer-Intern---Albuquerque--NM_R0252335</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5159,7 +5167,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -5174,7 +5182,7 @@
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5194,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
+          <t>University - 2027 Summer Games Software Developer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5217,7 +5225,7 @@
       <c r="H57" s="4" t="inlineStr"/>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>R0252273</t>
+          <t>R0252274</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -5227,7 +5235,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Software-Developer-Intern---Lexington--MA_R0252274</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5242,7 +5250,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
@@ -5257,7 +5265,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5277,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer, Junior</t>
+          <t>University - 2027 Summer Games Systems Engineer Intern - Lexington, MA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>McLean, VA</t>
+          <t>Lexington, MA</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5289,18 +5297,18 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>R0248060</t>
+          <t>R0252273</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -5310,7 +5318,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/Lexington-MA/University---2027-Summer-Games-Systems-Engineer-Intern---Lexington--MA_R0252273</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5325,7 +5333,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 17:31 UTC</t>
+          <t>2026-10-31 16:34 UTC</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5340,7 +5348,7 @@
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
@@ -5352,17 +5360,17 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Model-Based Systems Engineer, Junior</t>
+          <t>Full Stack Software Engineer, Junior</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>El Segundo, CA</t>
+          <t>McLean, VA</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5377,58 +5385,141 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
       <c r="I59" s="4" t="inlineStr">
         <is>
+          <t>R0248060</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/McLean-VA/Full-Stack-Software-Engineer--Junior_R0248060</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:34 UTC</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Model-Based Systems Engineer, Junior</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>El Segundo, CA</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
           <t>R0249353</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>workday</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>https://bah.wd1.myworkdayjobs.com/BAH_Jobs/job/El-Segundo-CA/Model-Based-Systems-Engineer--Junior_R0249353</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>☐ Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-30 17:31 UTC</t>
-        </is>
-      </c>
-      <c r="O59" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>☐ Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:34 UTC</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Historical sponsorship lookup was unavailable; no reliable current statement found.</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q59"/>
+  <autoFilter ref="A1:Q60"/>
   <dataValidations count="2">
     <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Applied" error="Select a value from the list" type="list">
       <formula1>"☐ Not Applied,☑ Applied"</formula1>
@@ -5496,6 +5587,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
